--- a/ui_runner/templates/graded_analysis_tabs_2026-06-18.xlsx
+++ b/ui_runner/templates/graded_analysis_tabs_2026-06-18.xlsx
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" t="n">
         <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="3">
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>91</v>
+        <v>377</v>
       </c>
       <c r="E4" t="n">
-        <v>45</v>
+        <v>124</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>253</v>
       </c>
       <c r="G4" t="n">
-        <v>49.5</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="5">
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7" t="n">
-        <v>58.3</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="8">
@@ -645,16 +645,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="G8" t="n">
-        <v>69.2</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="9">
@@ -674,16 +674,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" t="n">
         <v>20</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>57.1</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="10">
@@ -703,16 +703,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83</v>
+        <v>263</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>156</v>
       </c>
       <c r="G10" t="n">
-        <v>77.09999999999999</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="11">
@@ -732,16 +732,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>585</v>
+        <v>670</v>
       </c>
       <c r="E11" t="n">
-        <v>372</v>
+        <v>422</v>
       </c>
       <c r="F11" t="n">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="G11" t="n">
-        <v>63.6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>67</v>
+        <v>67.7</v>
       </c>
     </row>
     <row r="13">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F13" t="n">
         <v>29</v>
       </c>
       <c r="G13" t="n">
-        <v>52.5</v>
+        <v>54.7</v>
       </c>
     </row>
     <row r="14">
@@ -819,16 +819,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="E14" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="G14" t="n">
-        <v>22.3</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="15">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F15" t="n">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="G15" t="n">
-        <v>20.9</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="16">
@@ -877,16 +877,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G16" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="17">
@@ -906,16 +906,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2343</v>
+        <v>3709</v>
       </c>
       <c r="E17" t="n">
-        <v>498</v>
+        <v>646</v>
       </c>
       <c r="F17" t="n">
-        <v>1845</v>
+        <v>3063</v>
       </c>
       <c r="G17" t="n">
-        <v>21.3</v>
+        <v>17.4</v>
       </c>
     </row>
   </sheetData>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85.7</v>
+        <v>51.2</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
         <v>70.59999999999999</v>
@@ -1148,10 +1148,10 @@
         <v>36</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="R2" t="n">
         <v>67.90000000000001</v>
@@ -1159,17 +1159,20 @@
       <c r="S2" t="n">
         <v>28</v>
       </c>
+      <c r="T2" t="n">
+        <v>19</v>
+      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>87.5</v>
+        <v>52.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="Z2" t="n">
         <v>44.4</v>
@@ -1193,8 +1196,11 @@
           <t>Above Avg</t>
         </is>
       </c>
+      <c r="B3" t="n">
+        <v>15.3</v>
+      </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1214,20 +1220,29 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
+      <c r="P3" t="n">
+        <v>8.5</v>
+      </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="n">
+        <v>24.3</v>
+      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
+      <c r="X3" t="n">
+        <v>32</v>
+      </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1339,8 +1354,11 @@
           <t>Below Avg</t>
         </is>
       </c>
+      <c r="B5" t="n">
+        <v>13</v>
+      </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1360,20 +1378,29 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
+      <c r="P5" t="n">
+        <v>12.8</v>
+      </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="n">
+        <v>42.9</v>
+      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
+      <c r="X5" t="n">
+        <v>25</v>
+      </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1450,76 +1477,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77.09999999999999</v>
+        <v>40.7</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>263</v>
       </c>
       <c r="D7" t="n">
-        <v>63.6</v>
+        <v>63</v>
       </c>
       <c r="E7" t="n">
-        <v>585</v>
+        <v>670</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>67.7</v>
       </c>
       <c r="G7" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="H7" t="n">
-        <v>52.5</v>
+        <v>54.7</v>
       </c>
       <c r="I7" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J7" t="n">
-        <v>22.3</v>
+        <v>23.5</v>
       </c>
       <c r="K7" t="n">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="L7" t="n">
-        <v>20.9</v>
+        <v>19.5</v>
       </c>
       <c r="M7" t="n">
-        <v>230</v>
+        <v>256</v>
       </c>
       <c r="N7" t="n">
-        <v>26.6</v>
+        <v>26.8</v>
       </c>
       <c r="O7" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="P7" t="n">
-        <v>21.3</v>
+        <v>17.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>2343</v>
+        <v>3709</v>
       </c>
       <c r="R7" t="n">
-        <v>66</v>
+        <v>66.7</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="T7" t="n">
-        <v>49.5</v>
+        <v>32.9</v>
       </c>
       <c r="U7" t="n">
-        <v>91</v>
+        <v>377</v>
       </c>
       <c r="V7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>69.2</v>
+        <v>36.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="Z7" t="n">
         <v>50</v>
@@ -1534,16 +1561,16 @@
         <v>13</v>
       </c>
       <c r="AD7" t="n">
-        <v>58.3</v>
+        <v>56.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="AF7" t="n">
-        <v>57.1</v>
+        <v>54.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
